--- a/data/BZT_Hinweise.xlsx
+++ b/data/BZT_Hinweise.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Erläuterung" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fussnotentexte" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fussnoten_AnlageII" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hinweise" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Abweichungen" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Erläuterung" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Fussnotentexte" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Fussnoten_AnlageII" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Hinweise" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Abweichungen" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Fussnotentexte'!$A$1:$G$6</definedName>
@@ -450,9 +450,7 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr"/>
-    </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -460,9 +458,7 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr"/>
-    </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
@@ -519,9 +515,7 @@
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr"/>
-    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
@@ -599,9 +593,7 @@
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="inlineStr"/>
-    </row>
+    <row r="25"/>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
@@ -35809,7 +35801,7 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>bitte prüfen</t>
+          <t>korrekt</t>
         </is>
       </c>
     </row>
@@ -35860,7 +35852,7 @@
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>bitte prüfen</t>
+          <t>korrekt</t>
         </is>
       </c>
     </row>
@@ -35911,7 +35903,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>bitte prüfen</t>
+          <t>korrekt</t>
         </is>
       </c>
     </row>
@@ -35958,7 +35950,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>bitte prüfen</t>
+          <t>korrekt</t>
         </is>
       </c>
     </row>
@@ -36005,7 +35997,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>bitte prüfen</t>
+          <t>korrekt</t>
         </is>
       </c>
     </row>
@@ -36056,7 +36048,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>bitte prüfen</t>
+          <t>korrekt</t>
         </is>
       </c>
     </row>
@@ -36099,7 +36091,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>bitte prüfen</t>
+          <t>korrekt</t>
         </is>
       </c>
     </row>
@@ -36150,7 +36142,7 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>bitte prüfen</t>
+          <t>korrekt</t>
         </is>
       </c>
     </row>
@@ -36201,7 +36193,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>bitte prüfen</t>
+          <t>korrekt</t>
         </is>
       </c>
     </row>
@@ -36252,7 +36244,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>bitte prüfen</t>
+          <t>korrekt</t>
         </is>
       </c>
     </row>
@@ -36295,7 +36287,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>bitte prüfen</t>
+          <t>korrekt</t>
         </is>
       </c>
     </row>
@@ -36350,7 +36342,7 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>bitte prüfen</t>
+          <t>korrekt</t>
         </is>
       </c>
     </row>
@@ -36401,7 +36393,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>bitte prüfen</t>
+          <t>korrekt</t>
         </is>
       </c>
     </row>
@@ -36452,7 +36444,7 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>bitte prüfen</t>
+          <t>korrekt</t>
         </is>
       </c>
     </row>
@@ -36499,7 +36491,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>bitte prüfen</t>
+          <t>korrekt</t>
         </is>
       </c>
     </row>
@@ -36546,7 +36538,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>bitte prüfen</t>
+          <t>korrekt</t>
         </is>
       </c>
     </row>
@@ -36593,7 +36585,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>bitte prüfen</t>
+          <t>korrekt</t>
         </is>
       </c>
     </row>
@@ -36640,7 +36632,7 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>bitte prüfen</t>
+          <t>korrekt</t>
         </is>
       </c>
     </row>
@@ -36691,7 +36683,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>bitte prüfen</t>
+          <t>korrekt</t>
         </is>
       </c>
     </row>
@@ -36738,7 +36730,7 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>bitte prüfen</t>
+          <t>korrekt</t>
         </is>
       </c>
     </row>
@@ -36785,7 +36777,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>bitte prüfen</t>
+          <t>korrekt</t>
         </is>
       </c>
     </row>
@@ -36840,7 +36832,7 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>bitte prüfen</t>
+          <t>korrekt</t>
         </is>
       </c>
     </row>
@@ -36883,7 +36875,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>bitte prüfen</t>
+          <t>korrekt</t>
         </is>
       </c>
     </row>
@@ -36926,7 +36918,7 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>bitte prüfen</t>
+          <t>korrekt</t>
         </is>
       </c>
     </row>
